--- a/Side Bar Files/GWD Data/Pump Cover.xlsx
+++ b/Side Bar Files/GWD Data/Pump Cover.xlsx
@@ -63,7 +63,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Cambria"/>
         <family val="2"/>
       </rPr>
       <t>m</t>
@@ -73,7 +73,7 @@
         <vertAlign val="superscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Cambria"/>
         <family val="2"/>
       </rPr>
       <t>2</t>
@@ -90,7 +90,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Cambria"/>
         <family val="2"/>
       </rPr>
       <t>m</t>
@@ -100,7 +100,7 @@
         <vertAlign val="superscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Cambria"/>
         <family val="2"/>
       </rPr>
       <t>3</t>
@@ -213,7 +213,7 @@
   <numFmts count="1">
     <numFmt numFmtId="177" formatCode="0.00;[Red]0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -235,37 +235,23 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Cambria"/>
       <family val="2"/>
     </font>
     <font>
       <vertAlign val="superscript"/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -426,25 +412,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -453,7 +425,7 @@
   </cellStyleXfs>
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -462,22 +434,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
@@ -492,19 +464,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -519,11 +491,11 @@
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -620,7 +592,6 @@
       <sheetName val="GI Works"/>
       <sheetName val="Gravel for TWC"/>
       <sheetName val="Gutter&amp;Clamp"/>
-      <sheetName val="HDPE Pipe PRICE"/>
       <sheetName val="HP Erection and Pullout"/>
       <sheetName val="HP Repair Labour"/>
       <sheetName val="HP Repair Spares"/>
@@ -640,9 +611,11 @@
       <sheetName val="PVC Fittings PRICE"/>
       <sheetName val="PVC on Wall (Concealed) PRICE"/>
       <sheetName val="PVC on Wall PRICE"/>
+      <sheetName val="PVC on Wall"/>
+      <sheetName val="PVC wo Trench PRICE"/>
       <sheetName val="PVC wo Trench"/>
+      <sheetName val="PVC With Trench PRICE"/>
       <sheetName val="PVC With Trench"/>
-      <sheetName val="PVC With Trench PRICE"/>
       <sheetName val="Scaffolding"/>
       <sheetName val="Services"/>
       <sheetName val="TW Casing Pipes"/>
@@ -651,6 +624,9 @@
       <sheetName val="Water Tank"/>
       <sheetName val="Well Protection"/>
       <sheetName val="WTP"/>
+      <sheetName val="Derived"/>
+      <sheetName val="LMR"/>
+      <sheetName val="PAMR39"/>
       <sheetName val="ZCost Index"/>
     </sheetNames>
     <sheetDataSet>
@@ -698,6 +674,10 @@
       <sheetData sheetId="41"/>
       <sheetData sheetId="42"/>
       <sheetData sheetId="43"/>
+      <sheetData sheetId="44"/>
+      <sheetData sheetId="45"/>
+      <sheetData sheetId="46"/>
+      <sheetData sheetId="47"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -999,7 +979,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C82D10ED-C2B8-4A91-9624-E5C3CC69B9A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D373A3C2-364D-48C6-B2EB-9DB32249BAA6}">
   <dimension ref="A1:J39"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/Pump Cover.xlsx
+++ b/Side Bar Files/GWD Data/Pump Cover.xlsx
@@ -979,7 +979,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D373A3C2-364D-48C6-B2EB-9DB32249BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FA39988-D759-44A3-A4FF-4E251455BAA6}">
   <dimension ref="A1:J39"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/Pump Cover.xlsx
+++ b/Side Bar Files/GWD Data/Pump Cover.xlsx
@@ -221,13 +221,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,6 +232,13 @@
       <color theme="1"/>
       <name val="Cambria"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -269,7 +269,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -278,50 +278,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -344,6 +300,44 @@
       </bottom>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -363,52 +357,6 @@
       <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFDEE2E6"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFDEE2E6"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFDEE2E6"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFDEE2E6"/>
       </bottom>
     </border>
   </borders>
@@ -423,70 +371,52 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
-      <alignment/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -624,10 +554,10 @@
       <sheetName val="Water Tank"/>
       <sheetName val="Well Protection"/>
       <sheetName val="WTP"/>
-      <sheetName val="Derived"/>
-      <sheetName val="LMR"/>
-      <sheetName val="PAMR39"/>
-      <sheetName val="ZCost Index"/>
+      <sheetName val="zCost Index"/>
+      <sheetName val="zDerived"/>
+      <sheetName val="zLMR"/>
+      <sheetName val="zPAMR39"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -979,7 +909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FA39988-D759-44A3-A4FF-4E251455BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4700883F-DA04-4BAE-82B9-D5F5DC4EBAA6}">
   <dimension ref="A1:J39"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
@@ -1036,17 +966,17 @@
       <c r="B3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="3"/>
       <c r="J3" s="4"/>
     </row>
     <row r="4" spans="1:10" ht="12.75">
-      <c r="A4" s="11"/>
+      <c r="A4" s="10"/>
       <c r="B4" s="5" t="s">
         <v>12</v>
       </c>
@@ -1071,7 +1001,7 @@
       <c r="J4" s="4"/>
     </row>
     <row r="5" spans="1:10" ht="12.75">
-      <c r="A5" s="12"/>
+      <c r="A5" s="11"/>
       <c r="B5" s="5" t="s">
         <v>7</v>
       </c>
@@ -1101,17 +1031,17 @@
       <c r="B6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="13"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="3"/>
       <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:10" ht="12.75">
-      <c r="A7" s="11"/>
+      <c r="A7" s="10"/>
       <c r="B7" s="5" t="s">
         <v>15</v>
       </c>
@@ -1136,7 +1066,7 @@
       <c r="J7" s="4"/>
     </row>
     <row r="8" spans="1:10" ht="12.75">
-      <c r="A8" s="12"/>
+      <c r="A8" s="11"/>
       <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
@@ -1166,17 +1096,17 @@
       <c r="B9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="13"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="3"/>
       <c r="J9" s="4"/>
     </row>
     <row r="10" spans="1:10" ht="12.75">
-      <c r="A10" s="11"/>
+      <c r="A10" s="10"/>
       <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
@@ -1201,7 +1131,7 @@
       <c r="J10" s="4"/>
     </row>
     <row r="11" spans="1:10" ht="12.75">
-      <c r="A11" s="12"/>
+      <c r="A11" s="11"/>
       <c r="B11" s="5" t="s">
         <v>7</v>
       </c>
@@ -1231,17 +1161,17 @@
       <c r="B12" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="13"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="3"/>
       <c r="J12" s="4"/>
     </row>
     <row r="13" spans="1:10" ht="12.75">
-      <c r="A13" s="11"/>
+      <c r="A13" s="10"/>
       <c r="B13" s="5" t="s">
         <v>19</v>
       </c>
@@ -1264,7 +1194,7 @@
       <c r="J13" s="4"/>
     </row>
     <row r="14" spans="1:10" ht="12.75">
-      <c r="A14" s="11"/>
+      <c r="A14" s="10"/>
       <c r="B14" s="5" t="s">
         <v>20</v>
       </c>
@@ -1287,7 +1217,7 @@
       <c r="J14" s="4"/>
     </row>
     <row r="15" spans="1:10" ht="12.75">
-      <c r="A15" s="12"/>
+      <c r="A15" s="11"/>
       <c r="B15" s="5" t="s">
         <v>7</v>
       </c>
@@ -1317,17 +1247,17 @@
       <c r="B16" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="3"/>
       <c r="J16" s="4"/>
     </row>
     <row r="17" spans="1:10" ht="12.75">
-      <c r="A17" s="11"/>
+      <c r="A17" s="10"/>
       <c r="B17" s="5" t="s">
         <v>23</v>
       </c>
@@ -1355,7 +1285,7 @@
       <c r="J17" s="4"/>
     </row>
     <row r="18" spans="1:10" ht="12.75">
-      <c r="A18" s="11"/>
+      <c r="A18" s="10"/>
       <c r="B18" s="5" t="s">
         <v>27</v>
       </c>
@@ -1376,7 +1306,7 @@
       <c r="J18" s="4"/>
     </row>
     <row r="19" spans="1:10" ht="12.75">
-      <c r="A19" s="11"/>
+      <c r="A19" s="10"/>
       <c r="B19" s="5" t="s">
         <v>28</v>
       </c>
@@ -1397,7 +1327,7 @@
       <c r="J19" s="4"/>
     </row>
     <row r="20" spans="1:10" ht="12.75">
-      <c r="A20" s="11"/>
+      <c r="A20" s="10"/>
       <c r="B20" s="5" t="s">
         <v>29</v>
       </c>
@@ -1418,7 +1348,7 @@
       <c r="J20" s="4"/>
     </row>
     <row r="21" spans="1:10" ht="12.75">
-      <c r="A21" s="11"/>
+      <c r="A21" s="10"/>
       <c r="B21" s="5" t="s">
         <v>30</v>
       </c>
@@ -1439,7 +1369,7 @@
       <c r="J21" s="4"/>
     </row>
     <row r="22" spans="1:10" ht="12.75">
-      <c r="A22" s="11"/>
+      <c r="A22" s="10"/>
       <c r="B22" s="5" t="s">
         <v>31</v>
       </c>
@@ -1460,7 +1390,7 @@
       <c r="J22" s="4"/>
     </row>
     <row r="23" spans="1:10" ht="12.75">
-      <c r="A23" s="12"/>
+      <c r="A23" s="11"/>
       <c r="B23" s="5" t="s">
         <v>32</v>
       </c>
@@ -1495,17 +1425,17 @@
       <c r="B24" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="13"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="3"/>
       <c r="J24" s="4"/>
     </row>
     <row r="25" spans="1:10" ht="12.75">
-      <c r="A25" s="11"/>
+      <c r="A25" s="10"/>
       <c r="B25" s="5" t="s">
         <v>35</v>
       </c>
@@ -1529,7 +1459,7 @@
       <c r="J25" s="4"/>
     </row>
     <row r="26" spans="1:10" ht="12.75">
-      <c r="A26" s="11"/>
+      <c r="A26" s="10"/>
       <c r="B26" s="5"/>
       <c r="C26" s="4">
         <v>4</v>
@@ -1550,13 +1480,13 @@
       <c r="J26" s="4"/>
     </row>
     <row r="27" spans="1:10" ht="12.75">
-      <c r="A27" s="12"/>
+      <c r="A27" s="11"/>
       <c r="B27" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
-      <c r="E27" s="14"/>
+      <c r="E27" s="12"/>
       <c r="F27" s="4"/>
       <c r="G27" s="6">
         <f>SUM(G26)</f>
@@ -1580,25 +1510,25 @@
       <c r="B28" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="13"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="3"/>
     </row>
     <row r="29" spans="1:10" ht="12.75">
-      <c r="A29" s="12"/>
-      <c r="B29" s="9"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="5"/>
       <c r="C29" s="4">
         <v>1</v>
       </c>
       <c r="D29" s="4">
         <v>1.50</v>
       </c>
-      <c r="E29" s="15">
+      <c r="E29" s="13">
         <v>1.50</v>
       </c>
       <c r="F29" s="4"/>
@@ -1624,17 +1554,17 @@
       <c r="B30" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="13"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="3"/>
     </row>
     <row r="31" spans="1:10" ht="12.75">
-      <c r="A31" s="12"/>
+      <c r="A31" s="11"/>
       <c r="B31" s="5"/>
       <c r="C31" s="4">
         <v>3</v>
@@ -1649,7 +1579,7 @@
       <c r="H31" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="4">
         <v>30.15</v>
       </c>
       <c r="J31" s="7">
@@ -1664,17 +1594,17 @@
       <c r="B32" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="13"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="3"/>
     </row>
     <row r="33" spans="1:10" ht="12.75">
-      <c r="A33" s="12"/>
+      <c r="A33" s="11"/>
       <c r="B33" s="5"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -1686,7 +1616,7 @@
       <c r="H33" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="4">
         <v>910.62</v>
       </c>
       <c r="J33" s="7">
@@ -1701,18 +1631,18 @@
       <c r="B34" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="13"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="3"/>
     </row>
     <row r="35" spans="1:10" ht="12.75">
-      <c r="A35" s="11"/>
-      <c r="B35" s="9" t="s">
+      <c r="A35" s="10"/>
+      <c r="B35" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C35" s="8">
@@ -1728,7 +1658,7 @@
       <c r="H35" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="I35" s="16">
+      <c r="I35" s="4">
         <f>[1]Lock!F16</f>
         <v>641.15</v>
       </c>
@@ -1738,17 +1668,17 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="12.75">
-      <c r="A36" s="12"/>
-      <c r="B36" s="9" t="s">
+      <c r="A36" s="11"/>
+      <c r="B36" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="16">
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="4">
         <f>[1]Lock!F24</f>
         <v>27.042750000000002</v>
       </c>
@@ -1758,52 +1688,52 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="12.75">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="18">
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="15">
         <f>SUM(J3:J34,J36)</f>
         <v>6112.3343699999996</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="12.75">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="18">
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="15">
         <f>SUM(J35)</f>
         <v>641.15</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="12.75">
-      <c r="A39" s="19" t="s">
+      <c r="A39" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B39" s="20"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
-      <c r="J39" s="21"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="30">
